--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_h_6.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_h_6.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02257777422214252</v>
+        <v>0.01715790756174439</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008439159269661285</v>
+        <v>0.008432782635230575</v>
       </c>
       <c r="C2" t="n">
-        <v>37777662</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>37777662</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>26403683</v>
+        <v>4202989</v>
       </c>
       <c r="L2" t="n">
-        <v>14892759</v>
+        <v>2221824</v>
       </c>
       <c r="M2" t="n">
-        <v>3599903</v>
+        <v>496230</v>
       </c>
       <c r="N2" t="n">
-        <v>161114</v>
+        <v>12958</v>
       </c>
       <c r="O2" t="n">
-        <v>2217406</v>
+        <v>297722</v>
       </c>
       <c r="P2" t="n">
-        <v>871767</v>
+        <v>115395</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999850988388062</v>
+        <v>0.9999382495880127</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8754192590713501</v>
+        <v>0.8282104134559631</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7447059154510498</v>
+        <v>0.6609899997711182</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6822450757026672</v>
+        <v>0.5715236663818359</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3907603323459625</v>
+        <v>0.1461373567581177</v>
       </c>
       <c r="V2" t="n">
-        <v>0.731627345085144</v>
+        <v>0.6312658190727234</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8215180039405823</v>
+        <v>0.7615072131156921</v>
       </c>
       <c r="X2" t="n">
-        <v>37777662</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>37777662</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>28768914</v>
+        <v>4796855</v>
       </c>
       <c r="AG2" t="n">
-        <v>17794252</v>
+        <v>2983951</v>
       </c>
       <c r="AH2" t="n">
-        <v>4795649</v>
+        <v>801380</v>
       </c>
       <c r="AI2" t="n">
-        <v>353654</v>
+        <v>59049</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2754762</v>
+        <v>459641</v>
       </c>
       <c r="AK2" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9564045071601868</v>
+        <v>0.9560109972953796</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113450646400452</v>
+        <v>0.9115679264068604</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582964539527893</v>
+        <v>0.8585426211357117</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6622424125671387</v>
+        <v>0.6615541577339172</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020413160324097</v>
+        <v>0.9020492434501648</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314349889755249</v>
+        <v>0.9314607977867126</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.005601214642148763</v>
+        <v>0.004156408320834821</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002024109024678931</v>
+        <v>0.002022202495942296</v>
       </c>
       <c r="C3" t="n">
-        <v>383</v>
+        <v>362</v>
       </c>
       <c r="D3" t="n">
-        <v>26403683</v>
+        <v>4202989</v>
       </c>
       <c r="E3" t="n">
-        <v>3555547</v>
+        <v>786402</v>
       </c>
       <c r="F3" t="n">
-        <v>73147</v>
+        <v>17626</v>
       </c>
       <c r="G3" t="n">
-        <v>6415</v>
+        <v>1249</v>
       </c>
       <c r="H3" t="n">
-        <v>4866</v>
+        <v>953</v>
       </c>
       <c r="I3" t="n">
-        <v>171</v>
+        <v>27</v>
       </c>
       <c r="J3" t="n">
-        <v>59940176</v>
+        <v>10016232</v>
       </c>
       <c r="K3" t="n">
-        <v>63916685</v>
+        <v>10448197</v>
       </c>
       <c r="L3" t="n">
-        <v>73058502</v>
+        <v>11910808</v>
       </c>
       <c r="M3" t="n">
-        <v>90449594</v>
+        <v>15022539</v>
       </c>
       <c r="N3" t="n">
-        <v>96932751</v>
+        <v>16164544</v>
       </c>
       <c r="O3" t="n">
-        <v>93849610</v>
+        <v>15645756</v>
       </c>
       <c r="P3" t="n">
-        <v>96368976</v>
+        <v>16100020</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8788276314735413</v>
+        <v>0.8389856219291687</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7616033554077148</v>
+        <v>0.6775386333465576</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6437416076660156</v>
+        <v>0.5307085514068604</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3014553189277649</v>
+        <v>0.1450349241495132</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7257310748100281</v>
+        <v>0.5838384628295898</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7515071034431458</v>
+        <v>0.5965415835380554</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>28768914</v>
+        <v>4796855</v>
       </c>
       <c r="Z3" t="n">
-        <v>1183340</v>
+        <v>197460</v>
       </c>
       <c r="AA3" t="n">
-        <v>50881</v>
+        <v>8429</v>
       </c>
       <c r="AB3" t="n">
-        <v>40695</v>
+        <v>6823</v>
       </c>
       <c r="AC3" t="n">
-        <v>202</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>59940738</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>66362824</v>
+        <v>11099274</v>
       </c>
       <c r="AG3" t="n">
-        <v>76432907</v>
+        <v>12760866</v>
       </c>
       <c r="AH3" t="n">
-        <v>91334490</v>
+        <v>15262528</v>
       </c>
       <c r="AI3" t="n">
-        <v>97003575</v>
+        <v>16210047</v>
       </c>
       <c r="AJ3" t="n">
-        <v>94363832</v>
+        <v>15769750</v>
       </c>
       <c r="AK3" t="n">
-        <v>96478850</v>
+        <v>16122905</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575526118278503</v>
+        <v>0.9575310349464417</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099832773208618</v>
+        <v>0.9099469780921936</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8575672507286072</v>
+        <v>0.8570606708526611</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6617108583450317</v>
+        <v>0.660917341709137</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016014337539673</v>
+        <v>0.9013646841049194</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312928318977356</v>
+        <v>0.9312344789505005</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.05743308412491326</v>
+        <v>0.04654768569399213</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03193431931948926</v>
+        <v>0.03191410809705398</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>3539767</v>
+        <v>820671</v>
       </c>
       <c r="E4" t="n">
-        <v>14892759</v>
+        <v>2221824</v>
       </c>
       <c r="F4" t="n">
-        <v>987604</v>
+        <v>205989</v>
       </c>
       <c r="G4" t="n">
-        <v>34684</v>
+        <v>8697</v>
       </c>
       <c r="H4" t="n">
-        <v>92362</v>
+        <v>20355</v>
       </c>
       <c r="I4" t="n">
-        <v>7306</v>
+        <v>1722</v>
       </c>
       <c r="J4" t="n">
-        <v>562</v>
+        <v>390</v>
       </c>
       <c r="K4" t="n">
-        <v>3757503</v>
+        <v>871795</v>
       </c>
       <c r="L4" t="n">
-        <v>5105416</v>
+        <v>1139534</v>
       </c>
       <c r="M4" t="n">
-        <v>1676651</v>
+        <v>372028</v>
       </c>
       <c r="N4" t="n">
-        <v>251195</v>
+        <v>75712</v>
       </c>
       <c r="O4" t="n">
-        <v>813380</v>
+        <v>173905</v>
       </c>
       <c r="P4" t="n">
-        <v>189399</v>
+        <v>36140</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999925494194031</v>
+        <v>0.9999691247940063</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8771201372146606</v>
+        <v>0.8335632085800171</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7530598044395447</v>
+        <v>0.6691620349884033</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6624343395233154</v>
+        <v>0.5503604412078857</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3403470516204834</v>
+        <v>0.1455840617418289</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7286672592163086</v>
+        <v>0.606626570224762</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7849545478820801</v>
+        <v>0.6690049767494202</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1224375</v>
+        <v>206052</v>
       </c>
       <c r="Z4" t="n">
-        <v>17794252</v>
+        <v>2983951</v>
       </c>
       <c r="AA4" t="n">
-        <v>495701</v>
+        <v>82537</v>
       </c>
       <c r="AB4" t="n">
-        <v>32906</v>
+        <v>5520</v>
       </c>
       <c r="AC4" t="n">
-        <v>6840</v>
+        <v>1130</v>
       </c>
       <c r="AD4" t="n">
-        <v>408</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1311364</v>
+        <v>220718</v>
       </c>
       <c r="AG4" t="n">
-        <v>1731011</v>
+        <v>289476</v>
       </c>
       <c r="AH4" t="n">
-        <v>791755</v>
+        <v>132039</v>
       </c>
       <c r="AI4" t="n">
-        <v>180371</v>
+        <v>30209</v>
       </c>
       <c r="AJ4" t="n">
-        <v>299158</v>
+        <v>49911</v>
       </c>
       <c r="AK4" t="n">
-        <v>79525</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9569782018661499</v>
+        <v>0.9567704200744629</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106636047363281</v>
+        <v>0.9107567667961121</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8579316735267639</v>
+        <v>0.8578009605407715</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6619765162467957</v>
+        <v>0.6612355709075928</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018213152885437</v>
+        <v>0.9017068147659302</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313638806343079</v>
+        <v>0.9313476085662842</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>143048</v>
+        <v>34832</v>
       </c>
       <c r="E5" t="n">
-        <v>1315857</v>
+        <v>296881</v>
       </c>
       <c r="F5" t="n">
-        <v>3599903</v>
+        <v>496230</v>
       </c>
       <c r="G5" t="n">
-        <v>97455</v>
+        <v>24000</v>
       </c>
       <c r="H5" t="n">
-        <v>402846</v>
+        <v>75634</v>
       </c>
       <c r="I5" t="n">
-        <v>33026</v>
+        <v>7454</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3640529</v>
+        <v>806619</v>
       </c>
       <c r="L5" t="n">
-        <v>4661723</v>
+        <v>1057434</v>
       </c>
       <c r="M5" t="n">
-        <v>1992252</v>
+        <v>438803</v>
       </c>
       <c r="N5" t="n">
-        <v>373340</v>
+        <v>76386</v>
       </c>
       <c r="O5" t="n">
-        <v>838004</v>
+        <v>212217</v>
       </c>
       <c r="P5" t="n">
-        <v>288258</v>
+        <v>78045</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999942779541016</v>
+        <v>0.9999760985374451</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9242923259735107</v>
+        <v>0.8972164392471313</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9000481367111206</v>
+        <v>0.865460991859436</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9624543190002441</v>
+        <v>0.9503459334373474</v>
       </c>
       <c r="U5" t="n">
-        <v>0.993608832359314</v>
+        <v>0.990685760974884</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9831005930900574</v>
+        <v>0.9763544797897339</v>
       </c>
       <c r="W5" t="n">
-        <v>0.995111882686615</v>
+        <v>0.993007481098175</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>47971</v>
+        <v>8093</v>
       </c>
       <c r="Z5" t="n">
-        <v>510291</v>
+        <v>85757</v>
       </c>
       <c r="AA5" t="n">
-        <v>4795649</v>
+        <v>801380</v>
       </c>
       <c r="AB5" t="n">
-        <v>59673</v>
+        <v>9985</v>
       </c>
       <c r="AC5" t="n">
-        <v>174773</v>
+        <v>29185</v>
       </c>
       <c r="AD5" t="n">
-        <v>3798</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1275298</v>
+        <v>212753</v>
       </c>
       <c r="AG5" t="n">
-        <v>1760230</v>
+        <v>295307</v>
       </c>
       <c r="AH5" t="n">
-        <v>796506</v>
+        <v>133653</v>
       </c>
       <c r="AI5" t="n">
-        <v>180800</v>
+        <v>30295</v>
       </c>
       <c r="AJ5" t="n">
-        <v>300648</v>
+        <v>50298</v>
       </c>
       <c r="AK5" t="n">
-        <v>79702</v>
+        <v>13302</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735293984413147</v>
+        <v>0.9734548926353455</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642724394798279</v>
+        <v>0.9641887545585632</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837465286254883</v>
+        <v>0.9837294220924377</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963039755821228</v>
+        <v>0.9962948560714722</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938619136810303</v>
+        <v>0.9938633441925049</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983705282211304</v>
+        <v>0.9983736872673035</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>70161</v>
+        <v>15082</v>
       </c>
       <c r="E6" t="n">
-        <v>108502</v>
+        <v>20801</v>
       </c>
       <c r="F6" t="n">
-        <v>123986</v>
+        <v>28312</v>
       </c>
       <c r="G6" t="n">
-        <v>161114</v>
+        <v>12958</v>
       </c>
       <c r="H6" t="n">
-        <v>64706</v>
+        <v>11087</v>
       </c>
       <c r="I6" t="n">
-        <v>5912</v>
+        <v>1081</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>38703</v>
+        <v>6517</v>
       </c>
       <c r="Z6" t="n">
-        <v>32037</v>
+        <v>5368</v>
       </c>
       <c r="AA6" t="n">
-        <v>65304</v>
+        <v>10940</v>
       </c>
       <c r="AB6" t="n">
-        <v>353654</v>
+        <v>59049</v>
       </c>
       <c r="AC6" t="n">
-        <v>41870</v>
+        <v>6989</v>
       </c>
       <c r="AD6" t="n">
-        <v>2886</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>4319</v>
+        <v>1166</v>
       </c>
       <c r="E7" t="n">
-        <v>117707</v>
+        <v>33307</v>
       </c>
       <c r="F7" t="n">
-        <v>468455</v>
+        <v>113278</v>
       </c>
       <c r="G7" t="n">
-        <v>104498</v>
+        <v>38610</v>
       </c>
       <c r="H7" t="n">
-        <v>2217406</v>
+        <v>297722</v>
       </c>
       <c r="I7" t="n">
-        <v>142984</v>
+        <v>25856</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>147</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4857</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>177887</v>
+        <v>29802</v>
       </c>
       <c r="AB7" t="n">
-        <v>45504</v>
+        <v>7615</v>
       </c>
       <c r="AC7" t="n">
-        <v>2754762</v>
+        <v>459641</v>
       </c>
       <c r="AD7" t="n">
-        <v>72253</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>208</v>
+        <v>44</v>
       </c>
       <c r="E8" t="n">
-        <v>7803</v>
+        <v>2143</v>
       </c>
       <c r="F8" t="n">
-        <v>23459</v>
+        <v>6823</v>
       </c>
       <c r="G8" t="n">
-        <v>8143</v>
+        <v>3156</v>
       </c>
       <c r="H8" t="n">
-        <v>248600</v>
+        <v>65876</v>
       </c>
       <c r="I8" t="n">
-        <v>871767</v>
+        <v>115395</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>168</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>486</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1982</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1593</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>75473</v>
+        <v>12596</v>
       </c>
       <c r="AD8" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
